--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.82794471534306</v>
+        <v>1.434541016243247</v>
       </c>
       <c r="D2" t="n">
-        <v>8.791963192600701</v>
+        <v>1.428694018797614</v>
       </c>
       <c r="E2" t="n">
-        <v>21.78202135563032</v>
+        <v>3.539578470289927</v>
       </c>
       <c r="F2" t="n">
-        <v>19.48292637812787</v>
+        <v>3.16597553644578</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.02031781057431</v>
+        <v>10.40330164421833</v>
       </c>
       <c r="D3" t="n">
-        <v>60.86959792671571</v>
+        <v>9.891309663091302</v>
       </c>
       <c r="E3" t="n">
-        <v>21.78202135563032</v>
+        <v>3.539578470289927</v>
       </c>
       <c r="F3" t="n">
-        <v>19.48292637812787</v>
+        <v>3.16597553644578</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.66085157121417</v>
+        <v>5.469888380322304</v>
       </c>
       <c r="D4" t="n">
-        <v>21.4769053417771</v>
+        <v>3.489997118038779</v>
       </c>
       <c r="E4" t="n">
-        <v>21.78202135563032</v>
+        <v>3.539578470289927</v>
       </c>
       <c r="F4" t="n">
-        <v>19.48292637812787</v>
+        <v>3.16597553644578</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.70322773037748</v>
+        <v>9.376774506186342</v>
       </c>
       <c r="D5" t="n">
-        <v>22.77127638182792</v>
+        <v>3.700332412047037</v>
       </c>
       <c r="E5" t="n">
-        <v>21.78202135563032</v>
+        <v>3.539578470289927</v>
       </c>
       <c r="F5" t="n">
-        <v>19.48292637812787</v>
+        <v>3.16597553644578</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
